--- a/Result/profitability/2910.xlsx
+++ b/Result/profitability/2910.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>0.31375</v>
+        <v>0.3775</v>
       </c>
       <c r="N2" t="n">
-        <v>79.3</v>
+        <v>79.6225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32875</v>
+        <v>0.3825</v>
       </c>
       <c r="N3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.30375000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33375</v>
+        <v>0.3875</v>
       </c>
       <c r="N4" t="n">
-        <v>65.2475</v>
+        <v>64.38375000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3075</v>
+        <v>0.38375</v>
       </c>
       <c r="N5" t="n">
-        <v>56.41875</v>
+        <v>55.7575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.31375</v>
+        <v>0.345</v>
       </c>
       <c r="N6" t="n">
-        <v>48.195</v>
+        <v>47.5925</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26375</v>
+        <v>0.31375</v>
       </c>
       <c r="N7" t="n">
-        <v>40.09375</v>
+        <v>39.4775</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2375</v>
+        <v>0.2925</v>
       </c>
       <c r="N8" t="n">
-        <v>32.11125</v>
+        <v>31.1325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>145</v>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>120</v>
+      </c>
+      <c r="F75" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>74</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>50.82%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>63</v>
+      </c>
+      <c r="J75" t="n">
+        <v>136</v>
+      </c>
+      <c r="K75" t="n">
+        <v>128</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3462500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>86.37625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.517241379310345</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.829999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08650977792509118</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.289999999999992</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06013413663749001</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
